--- a/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N14_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N14_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>22.69678905534023</v>
+        <v>3.688228221492788</v>
       </c>
       <c r="D2" t="n">
-        <v>19.38824506342004</v>
+        <v>3.150589822805757</v>
       </c>
       <c r="E2" t="n">
-        <v>8.82730581434784</v>
+        <v>1.434437194831524</v>
       </c>
       <c r="F2" t="n">
-        <v>4.640090726311921</v>
+        <v>0.7540147430256871</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>10.41659813695202</v>
+        <v>1.692697197254703</v>
       </c>
       <c r="D3" t="n">
-        <v>11.55085419266796</v>
+        <v>1.877013806308544</v>
       </c>
       <c r="E3" t="n">
-        <v>8.82730581434784</v>
+        <v>1.434437194831524</v>
       </c>
       <c r="F3" t="n">
-        <v>4.640090726311921</v>
+        <v>0.7540147430256871</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>31.96914502302945</v>
+        <v>5.194986066242286</v>
       </c>
       <c r="D4" t="n">
-        <v>22.59825687565317</v>
+        <v>3.67221674229364</v>
       </c>
       <c r="E4" t="n">
-        <v>8.82730581434784</v>
+        <v>1.434437194831524</v>
       </c>
       <c r="F4" t="n">
-        <v>4.640090726311921</v>
+        <v>0.7540147430256871</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
